--- a/research/breed-intelligence-database.xlsx
+++ b/research/breed-intelligence-database.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Breed Groups Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Breed Intelligence DB'!$A$4:$O$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Breed Intelligence DB'!$A$4:$P$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -513,37 +513,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TechPup Breed Intelligence Database</t>
+          <t>TechPup HK Breed Intelligence Database</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Milestone 3: Breed &amp; Personality Intelligence System | 30 most common breeds</t>
+          <t>Milestone 3: Breed &amp; Personality Intelligence System | 30 breeds most common among Hong Kong dog owners</t>
         </is>
       </c>
     </row>
@@ -565,475 +566,505 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>HK Context</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Avg Weight (kg)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Lifespan</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Energy Level</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Training Difficulty</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Bonding Style</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Common Health Challenges</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Common Behavioral Challenges</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Primary Archetype</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Secondary Archetype</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Daily Activity Target (min)</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>TechPup v1 Coverage</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Golden Retriever</t>
+          <t>Poodle</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Sporting</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>10-12 yrs</t>
-        </is>
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>HK's #1 breed by owner share; Toy/Miniature variant dominates for apartment living, low-shedding coat</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Toy-Small</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>12-15 yrs</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Family-oriented</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Hip/elbow dysplasia, cancer risk</t>
-        </is>
-      </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Mouthiness, separation anxiety</t>
+          <t>Hip dysplasia, Addison's disease, dental issues</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>Social Butterfly</t>
+          <t>Boredom-driven mischief</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>Foodie</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
+          <t>Genius</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>Athlete</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Labrador Retriever</t>
+          <t>French Bulldog</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Sporting</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>#2 in HK; compact build and low exercise need make it ideal for small flats</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>10-12 yrs</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Family-oriented</t>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
         <is>
-          <t>Obesity, hip dysplasia</t>
+          <t>One-family</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>Chewing, food-stealing</t>
+          <t>Brachycephalic breathing, spinal issues, heat sensitivity</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
+          <t>Stubbornness</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>Zen Dog</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
           <t>Foodie</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>Social Butterfly</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="O6" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="10" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Cocker Spaniel</t>
+          <t>Shih Tzu</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Sporting</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>12-15 yrs</t>
-        </is>
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Long-standing HK household favourite across generations</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Medium-High</t>
+          <t>10-16 yrs</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>One-family</t>
-        </is>
-      </c>
       <c r="J7" s="12" t="inlineStr">
         <is>
-          <t>Ear infections, separation anxiety</t>
+          <t>Family-oriented</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Submissive urination, clinginess</t>
+          <t>Brachycephalic breathing, eye issues</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
+          <t>Stubbornness</t>
+        </is>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>Zen Dog</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="inlineStr">
+        <is>
           <t>Social Butterfly</t>
         </is>
       </c>
-      <c r="M7" s="12" t="inlineStr">
-        <is>
-          <t>Zen Dog</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="O7" s="10" t="inlineStr">
+      <c r="O7" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Maltese</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Sporting</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Popular with first-time and elderly HK owners for its gentle temperament</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Toy</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>12-15 yrs</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>12-14 yrs</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Active-owner bonded</t>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="J8" s="9" t="inlineStr">
         <is>
-          <t>Hip dysplasia, exercise-induced collapse</t>
+          <t>Family-oriented</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>Hyperactivity if under-exercised</t>
+          <t>Dental issues, separation anxiety</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>Athlete</t>
+          <t>Clinginess</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>Adventurer</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="O8" s="7" t="inlineStr">
+          <t>Social Butterfly</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>Zen Dog</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="10" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Beagle</t>
+          <t>Pomeranian</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Hound</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Small-Medium</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>12-15 yrs</t>
-        </is>
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Compact and photogenic; strong presence on HK pet social media</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Toy</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>12-16 yrs</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Challenging</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>Pack-oriented</t>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>Obesity, ear infections</t>
+          <t>One-person</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Scent-following escape, baying</t>
+          <t>Dental issues, tracheal collapse, luxating patella</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>Explorer</t>
+          <t>Vocal alerting</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>Foodie</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="O9" s="10" t="inlineStr">
+          <t>Social Butterfly</t>
+        </is>
+      </c>
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="O9" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Dachshund</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Hound</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>12-16 yrs</t>
-        </is>
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Smallest space footprint; popular in HK's highest-density districts</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Toy</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>2.5</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
+          <t>14-16 yrs</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>One-person</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>IVDD (spinal disc disease)</t>
-        </is>
-      </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>Stubbornness, digging</t>
+          <t>Dental issues, temperature sensitivity</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>Explorer</t>
+          <t>Wariness of strangers, yappiness</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
@@ -1041,1561 +1072,1671 @@
           <t>Guardian</t>
         </is>
       </c>
-      <c r="N10" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>Zen Dog</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="10" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Basset Hound</t>
+          <t>Yorkshire Terrier</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Hound</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Classic small-flat companion breed across HK Island and Kowloon</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Toy</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>13-16 yrs</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>10-12 yrs</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Low-Medium</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Challenging</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>Family-oriented</t>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>Obesity, ear infections, back problems</t>
+          <t>One-person</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Stubborn nose-led wandering</t>
+          <t>Dental issues, tracheal collapse</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>Zen Dog</t>
+          <t>Yappiness, fragility around children</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>Foodie</t>
-        </is>
-      </c>
-      <c r="N11" s="10" t="n">
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>Social Butterfly</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="P11" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Siberian Husky</t>
+          <t>Pug</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Working</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Medium-Large</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>12-14 yrs</t>
-        </is>
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Low exercise need suits HK's hot, humid climate, though heat care is essential</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Toy</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>12-15 yrs</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Challenging</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Pack-oriented</t>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
         <is>
-          <t>Hip dysplasia, eye disorders</t>
+          <t>Family-oriented</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>Escape artist, vocal/howling</t>
+          <t>Brachycephalic breathing, obesity, heat sensitivity</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>Athlete</t>
+          <t>Stubbornness</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>Adventurer</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
+          <t>Foodie</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>Zen Dog</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
+    <row r="13" ht="40" customHeight="1">
       <c r="A13" s="10" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Boxer</t>
+          <t>Cavalier King Charles Spaniel</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Working</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>10-12 yrs</t>
-        </is>
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Gentle and affectionate; steadily rising in HK over the last decade</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>12-15 yrs</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>Family-oriented</t>
         </is>
       </c>
-      <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>Heart conditions, cancer risk, heat sensitivity</t>
-        </is>
-      </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Jumping, exuberant play</t>
+          <t>Heart disease (MVD), syringomyelia</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
+          <t>Separation anxiety</t>
+        </is>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
           <t>Social Butterfly</t>
         </is>
       </c>
-      <c r="M13" s="12" t="inlineStr">
-        <is>
-          <t>Athlete</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="O13" s="10" t="inlineStr">
+      <c r="N13" s="12" t="inlineStr">
+        <is>
+          <t>Zen Dog</t>
+        </is>
+      </c>
+      <c r="O13" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="P13" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
+    <row r="14" ht="40" customHeight="1">
       <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Doberman Pinscher</t>
+          <t>Miniature Schnauzer</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Working</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>10-13 yrs</t>
-        </is>
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Popular low-shedding, alert small breed among HK families</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>12-14 yrs</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>One-family</t>
-        </is>
-      </c>
       <c r="J14" s="9" t="inlineStr">
         <is>
-          <t>Dilated cardiomyopathy, von Willebrand's disease</t>
+          <t>Family-oriented</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>Protectiveness without socialization</t>
+          <t>Pancreatitis, bladder stones</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
+          <t>Vocal alerting, stubbornness</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
           <t>Guardian</t>
         </is>
       </c>
-      <c r="M14" s="9" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Genius</t>
         </is>
       </c>
-      <c r="N14" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="O14" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
+    <row r="15" ht="40" customHeight="1">
       <c r="A15" s="10" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Great Dane</t>
+          <t>Bichon Frise</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Working</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Giant</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>8-10 yrs</t>
-        </is>
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Hypoallergenic coat valued by allergy-conscious HK owners</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
+          <t>14-15 yrs</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>Family-oriented</t>
         </is>
       </c>
-      <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>Bloat (GDV), short lifespan, joint issues</t>
-        </is>
-      </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Space-unaware leaning/sitting</t>
+          <t>Skin allergies, dental issues</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
+          <t>Separation anxiety</t>
+        </is>
+      </c>
+      <c r="M15" s="12" t="inlineStr">
+        <is>
+          <t>Social Butterfly</t>
+        </is>
+      </c>
+      <c r="N15" s="12" t="inlineStr">
+        <is>
           <t>Zen Dog</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr">
-        <is>
-          <t>Guardian</t>
-        </is>
-      </c>
-      <c r="N15" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="O15" s="10" t="inlineStr">
+      <c r="O15" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
+    <row r="16" ht="40" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Rottweiler</t>
+          <t>Dachshund</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Working</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="n">
+          <t>Toy &amp; Companion</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Miniature variant most common in HK; compact long-bodied build suits small homes</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>12-16 yrs</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>One-person</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>IVDD (spinal disc disease)</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>Stubbornness, digging</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>Explorer</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Pembroke Welsh Corgi</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Herding</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Social-media and 'Royal corgi' trend drove a sharp HK ownership rise since 2018</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>12-13 yrs</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Family-oriented</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>IVDD (long spine), obesity</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Nipping/herding instinct toward kids</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>Genius</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>Social Butterfly</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>9-10 yrs</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Medium-High</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>One-family</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>Hip/elbow dysplasia, cancer risk</t>
-        </is>
-      </c>
-      <c r="K16" s="9" t="inlineStr">
-        <is>
-          <t>Needs experienced handling</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>Guardian</t>
-        </is>
-      </c>
-      <c r="M16" s="9" t="inlineStr">
-        <is>
-          <t>Genius</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Yorkshire Terrier</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Terrier</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Toy</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>13-16 yrs</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
-        <is>
-          <t>One-person</t>
-        </is>
-      </c>
-      <c r="J17" s="12" t="inlineStr">
-        <is>
-          <t>Dental issues, tracheal collapse</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>Yappiness, fragility around children</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>Guardian</t>
-        </is>
-      </c>
-      <c r="M17" s="12" t="inlineStr">
-        <is>
-          <t>Social Butterfly</t>
-        </is>
-      </c>
-      <c r="N17" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O17" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>West Highland White Terrier</t>
+          <t>German Shepherd</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Terrier</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>13-15 yrs</t>
-        </is>
+          <t>Herding</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Popular among village-house and larger-flat owners in the New Territories</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>33</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Medium-High</t>
+          <t>9-13 yrs</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>Independent but loyal</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>Skin allergies</t>
+          <t>One-family</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Digging, hyperactivity</t>
+          <t>Hip/elbow dysplasia, degenerative myelopathy</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>Explorer</t>
+          <t>Protectiveness, destructive if bored</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>Adventurer</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
+          <t>Genius</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="10" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Jack Russell Terrier</t>
+          <t>Border Collie</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Terrier</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>13-16 yrs</t>
-        </is>
+          <t>Herding</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Favoured by HK's active hiking owners (Sai Kung, Lantau trail culture)</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>18</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
+          <t>12-15 yrs</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>Challenging</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>Active-owner bonded</t>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>Dental issues</t>
+          <t>One-person/family</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>High prey drive, escape artist</t>
+          <t>Hip dysplasia, collie eye anomaly</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
+          <t>Obsessive herding behaviors if under-stimulated</t>
+        </is>
+      </c>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>Genius</t>
+        </is>
+      </c>
+      <c r="N19" s="12" t="inlineStr">
+        <is>
           <t>Athlete</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr">
-        <is>
-          <t>Explorer</t>
-        </is>
-      </c>
-      <c r="N19" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="O19" s="10" t="inlineStr">
+      <c r="O19" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="P19" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
+    <row r="20" ht="40" customHeight="1">
       <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Chihuahua</t>
+          <t>Australian Shepherd</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Toy</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Toy</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>14-16 yrs</t>
-        </is>
+          <t>Herding</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Niche but growing among HK's active-lifestyle owners with regular trail access</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Medium-Large</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>25</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>12-15 yrs</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>One-person</t>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>Dental issues, temperature sensitivity</t>
+          <t>One-family</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>Wariness of strangers, yappiness</t>
+          <t>Hip dysplasia, eye disorders</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>Guardian</t>
+          <t>Needs a job or develops anxiety</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>Zen Dog</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="O20" s="7" t="inlineStr">
+          <t>Genius</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>Athlete</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="10" t="n">
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Pomeranian</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Toy</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Toy</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>12-16 yrs</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>Medium-High</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>One-person</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="inlineStr">
-        <is>
-          <t>Dental issues, tracheal collapse, luxating patella</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="inlineStr">
-        <is>
-          <t>Vocal alerting</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Golden Retriever</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Sporting</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Most popular large breed in HK; enduring family favourite</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>10-12 yrs</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Family-oriented</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>Hip/elbow dysplasia, cancer risk</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Mouthiness, separation anxiety</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
         <is>
           <t>Social Butterfly</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr">
-        <is>
-          <t>Guardian</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O21" s="10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>Foodie</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
       <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Maltese</t>
+          <t>Labrador Retriever</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Toy</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Toy</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>12-15 yrs</t>
-        </is>
+          <t>Sporting</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Steady HK presence; common choice as a family's first large dog</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>32</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>10-12 yrs</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>Family-oriented</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>Dental issues, separation anxiety</t>
-        </is>
-      </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>Clinginess</t>
+          <t>Obesity, hip dysplasia</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
+          <t>Chewing, food-stealing</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>Foodie</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
           <t>Social Butterfly</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
-        <is>
-          <t>Zen Dog</t>
-        </is>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="O22" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
+    <row r="23" ht="40" customHeight="1">
       <c r="A23" s="10" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Pug</t>
+          <t>Cocker Spaniel</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Toy</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Toy</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
+          <t>Sporting</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Long-running mid-size favourite in HK households</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>12-15 yrs</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>Low-Medium</t>
-        </is>
-      </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
-        <is>
-          <t>Family-oriented</t>
-        </is>
-      </c>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>Brachycephalic breathing, obesity, heat sensitivity</t>
+          <t>One-family</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Stubbornness</t>
+          <t>Ear infections, separation anxiety</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>Foodie</t>
+          <t>Submissive urination, clinginess</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
+          <t>Social Butterfly</t>
+        </is>
+      </c>
+      <c r="N23" s="12" t="inlineStr">
+        <is>
           <t>Zen Dog</t>
         </is>
       </c>
-      <c r="N23" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="O23" s="10" t="inlineStr">
+      <c r="O23" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="P23" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
+    <row r="24" ht="40" customHeight="1">
       <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>French Bulldog</t>
+          <t>Beagle</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Non-Sporting</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
+          <t>Hound</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Popular among HK families for its friendly, easygoing temperament</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Small-Medium</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>12-15 yrs</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>Pack-oriented</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>Obesity, ear infections</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>Scent-following escape, baying</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>Explorer</t>
+        </is>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>Foodie</t>
+        </is>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Italian Greyhound</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Hound</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Rising HK trend: sighthound elegance in a very apartment-compatible size</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="E24" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>10-12 yrs</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>Low-Medium</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="F25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>13-15 yrs</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>One-family</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>Brachycephalic breathing, spinal issues, heat sensitivity</t>
-        </is>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>Stubbornness</t>
-        </is>
-      </c>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>One-person</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>Fractures (fragile bones), cold sensitivity</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>Skittishness</t>
+        </is>
+      </c>
+      <c r="M25" s="12" t="inlineStr">
         <is>
           <t>Zen Dog</t>
         </is>
       </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>Foodie</t>
-        </is>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="N25" s="12" t="inlineStr">
+        <is>
+          <t>Explorer</t>
+        </is>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="P25" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Poodle</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Non-Sporting</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Medium-Large</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>12-15 yrs</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>Family-oriented</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>Hip dysplasia, Addison's disease</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>Boredom-driven mischief</t>
-        </is>
-      </c>
-      <c r="L25" s="6" t="inlineStr">
-        <is>
-          <t>Genius</t>
-        </is>
-      </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>Athlete</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="O25" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="32" customHeight="1">
+    <row r="26" ht="40" customHeight="1">
       <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Bulldog</t>
+          <t>Siberian Husky</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Non-Sporting</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>8-10 yrs</t>
-        </is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Popular for striking looks; needs careful heat management in HK's climate</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Medium-Large</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>22</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>12-14 yrs</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Family-oriented</t>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Challenging</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>Brachycephalic breathing, joint issues, heat sensitivity</t>
+          <t>Pack-oriented</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>Stubbornness</t>
+          <t>Hip dysplasia, eye disorders, heat intolerance</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>Zen Dog</t>
+          <t>Escape artist, vocal/howling</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>Foodie</t>
-        </is>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="O26" s="7" t="inlineStr">
+          <t>Adventurer</t>
+        </is>
+      </c>
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t>Athlete</t>
+        </is>
+      </c>
+      <c r="O26" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
+    <row r="27" ht="40" customHeight="1">
       <c r="A27" s="10" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Boston Terrier</t>
+          <t>Doberman Pinscher</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Non-Sporting</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>11-13 yrs</t>
-        </is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Present among HK owners seeking a guardian-companion breed</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>35</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>10-13 yrs</t>
         </is>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>Family-oriented</t>
-        </is>
-      </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>Brachycephalic breathing, eye issues</t>
+          <t>One-family</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Gas/flatulence, attention-seeking</t>
+          <t>Dilated cardiomyopathy, von Willebrand's disease</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>Social Butterfly</t>
+          <t>Protectiveness without socialization</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>Foodie</t>
-        </is>
-      </c>
-      <c r="N27" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="O27" s="10" t="inlineStr">
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>Genius</t>
+        </is>
+      </c>
+      <c r="O27" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="P27" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
+    <row r="28" ht="40" customHeight="1">
       <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Dalmatian</t>
+          <t>Rottweiler</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Non-Sporting</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Niche in HK; mostly village-house owners given its size and handling needs</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>11-13 yrs</t>
-        </is>
+      <c r="F28" s="7" t="n">
+        <v>45</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>9-10 yrs</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>Family-oriented</t>
-        </is>
-      </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>Deafness risk, urinary stones</t>
+          <t>One-family</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>Restlessness if under-exercised</t>
+          <t>Hip/elbow dysplasia, cancer risk</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>Athlete</t>
+          <t>Needs experienced handling</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>Adventurer</t>
-        </is>
-      </c>
-      <c r="N28" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="O28" s="7" t="inlineStr">
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="N28" s="9" t="inlineStr">
+        <is>
+          <t>Genius</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="32" customHeight="1">
+    <row r="29" ht="40" customHeight="1">
       <c r="A29" s="10" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>German Shepherd</t>
+          <t>Great Dane</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Herding</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>9-13 yrs</t>
-        </is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Rare in flats; seen mostly in New Territories village houses with outdoor space</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Giant</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>60</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
+          <t>8-10 yrs</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>Family-oriented</t>
+        </is>
+      </c>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>Bloat (GDV), short lifespan, joint issues</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>Space-unaware leaning/sitting</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr">
+        <is>
+          <t>Zen Dog</t>
+        </is>
+      </c>
+      <c r="N29" s="12" t="inlineStr">
+        <is>
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="P29" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Shiba Inu</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Spitz</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Rising sharply across HK and East Asia since 2020</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Small-Medium</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>13-16 yrs</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Challenging</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>One-person</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>Skin allergies</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>Independence, aloofness with strangers, 'Shiba scream'</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>Explorer</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>Guardian</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Samoyed</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Spitz</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Strong HK social-media following for its fluffy coat and 'smiling' expression</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>12-14 yrs</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>One-family</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="inlineStr">
-        <is>
-          <t>Hip/elbow dysplasia, degenerative myelopathy</t>
-        </is>
-      </c>
-      <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>Protectiveness, destructive if bored</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>Genius</t>
-        </is>
-      </c>
-      <c r="M29" s="12" t="inlineStr">
-        <is>
-          <t>Guardian</t>
-        </is>
-      </c>
-      <c r="N29" s="10" t="n">
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>Family-oriented</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>Hip dysplasia, heat intolerance (heavy coat)</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>Vocal, heavy shedding</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="inlineStr">
+        <is>
+          <t>Social Butterfly</t>
+        </is>
+      </c>
+      <c r="N31" s="12" t="inlineStr">
+        <is>
+          <t>Adventurer</t>
+        </is>
+      </c>
+      <c r="O31" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="O29" s="10" t="inlineStr">
+      <c r="P31" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Border Collie</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Herding</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>12-15 yrs</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>Very High</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>One-person/family</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr">
-        <is>
-          <t>Hip dysplasia, collie eye anomaly</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>Obsessive herding behaviors if under-stimulated</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>Genius</t>
-        </is>
-      </c>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>Athlete</t>
-        </is>
-      </c>
-      <c r="N30" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="O30" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Pembroke Welsh Corgi</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Herding</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>12-13 yrs</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Medium-High</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>Family-oriented</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>IVDD (long spine), obesity</t>
-        </is>
-      </c>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>Nipping/herding instinct toward kids</t>
-        </is>
-      </c>
-      <c r="L31" s="6" t="inlineStr">
-        <is>
-          <t>Genius</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="inlineStr">
-        <is>
-          <t>Social Butterfly</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="O31" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
+    <row r="32" ht="40" customHeight="1">
       <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Australian Shepherd</t>
+          <t>Jack Russell Terrier</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Herding</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Medium-Large</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>12-15 yrs</t>
-        </is>
+          <t>Terrier</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Niche among HK's active small-dog owners</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>7</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
+          <t>13-16 yrs</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
           <t>Very High</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>One-family</t>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Challenging</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>Hip dysplasia, eye disorders</t>
+          <t>Active-owner bonded</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>Needs a job or develops anxiety</t>
+          <t>Dental issues</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>Genius</t>
+          <t>High prey drive, escape artist</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr">
@@ -2603,70 +2744,75 @@
           <t>Athlete</t>
         </is>
       </c>
-      <c r="N32" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="O32" s="7" t="inlineStr">
+      <c r="N32" s="9" t="inlineStr">
+        <is>
+          <t>Explorer</t>
+        </is>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="P32" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1">
+    <row r="33" ht="40" customHeight="1">
       <c r="A33" s="4" t="n">
         <v>29</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
+          <t>Tong Gau</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Spitz</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Small-Medium</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>13-16 yrs</t>
-        </is>
+          <t>Native &amp; Local HK</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Native Hong Kong breed; resilient and hardy with a small but loyal following</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>18</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Medium-High</t>
+          <t>12-15 yrs</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Challenging</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>One-person</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Skin allergies</t>
+          <t>Family-oriented</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Independence, aloofness with strangers, 'Shiba scream'</t>
+          <t>Limited formal breed data; generally hardy constitution</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>Explorer</t>
+          <t>Wariness of strangers</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
@@ -2674,91 +2820,101 @@
           <t>Guardian</t>
         </is>
       </c>
-      <c r="N33" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>Zen Dog</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="4" t="n">
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Tong Gau</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Native HK</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Local Mixed Breed / Rescue</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Native &amp; Local HK</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Large share of HK's dog population via SPCA, HK Dog Rescue, and other NGO adoptions</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>12-15 yrs</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>Family-oriented</t>
         </is>
       </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>Limited formal breed data; generally hardy/resilient</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>Wariness of strangers</t>
-        </is>
-      </c>
-      <c r="L34" s="6" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>Generally good hybrid vigor; varies by individual</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>Adjustment period common post-adoption</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>Zen Dog</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="inlineStr">
         <is>
           <t>Guardian</t>
         </is>
       </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>Zen Dog</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="n">
+      <c r="O34" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O4"/>
+  <autoFilter ref="A4:P4"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2855,7 +3011,7 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Beagle, Dachshund, Shiba Inu, West Highland White Terrier, Jack Russell Terrier</t>
+          <t>Dachshund, Beagle, Shiba Inu, Italian Greyhound, Jack Russell Terrier</t>
         </is>
       </c>
     </row>
@@ -2887,7 +3043,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Border Collie, German Shepherd, Poodle, Australian Shepherd, Doberman Pinscher, Rottweiler, Pembroke Welsh Corgi</t>
+          <t>Poodle, Pembroke Welsh Corgi, German Shepherd, Border Collie, Australian Shepherd</t>
         </is>
       </c>
     </row>
@@ -2919,7 +3075,7 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Golden Retriever, Labrador Retriever, Boxer, Maltese, Boston Terrier, Cocker Spaniel, Pomeranian</t>
+          <t>Maltese, Pomeranian, Cavalier King Charles Spaniel, Bichon Frise, Golden Retriever, Cocker Spaniel, Samoyed</t>
         </is>
       </c>
     </row>
@@ -2951,7 +3107,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Siberian Husky, Brittany, Dalmatian, West Highland White Terrier</t>
+          <t>Siberian Husky, Samoyed</t>
         </is>
       </c>
     </row>
@@ -2983,7 +3139,7 @@
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Bulldog, French Bulldog, Basset Hound, Great Dane, Chihuahua, Pug, Tong Gau</t>
+          <t>French Bulldog, Shih Tzu, Italian Greyhound, Great Dane, Local Mixed Breed / Rescue, Tong Gau</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3171,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Doberman Pinscher, Rottweiler, German Shepherd, Chihuahua, Yorkshire Terrier, Shiba Inu, Tong Gau</t>
+          <t>Chihuahua, Yorkshire Terrier, Miniature Schnauzer, Doberman Pinscher, Rottweiler, Tong Gau</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3203,7 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Labrador Retriever, Beagle, Basset Hound, Pug, Bulldog, Boston Terrier, French Bulldog</t>
+          <t>Pug, Labrador Retriever, French Bulldog, Golden Retriever, Beagle</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3235,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Border Collie, Jack Russell Terrier, Siberian Husky, Dalmatian, Poodle, Australian Shepherd, Boxer</t>
+          <t>Jack Russell Terrier, Poodle, Border Collie, Australian Shepherd, Siberian Husky</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3117,7 +3273,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>30 breeds organized into 8 functional groups</t>
+          <t>30 HK-popular breeds organized into 8 functional groups</t>
         </is>
       </c>
     </row>
@@ -3146,51 +3302,51 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Sporting</t>
+          <t>Toy &amp; Companion</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Golden Retriever, Labrador Retriever, Cocker Spaniel, Brittany</t>
+          <t>Poodle, French Bulldog, Shih Tzu, Maltese, Pomeranian, Chihuahua, Yorkshire Terrier, Pug, Cavalier King Charles Spaniel, Miniature Schnauzer, Bichon Frise, Dachshund</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Hound</t>
+          <t>Herding</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Beagle, Dachshund, Basset Hound</t>
+          <t>Pembroke Welsh Corgi, German Shepherd, Border Collie, Australian Shepherd</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Working</t>
+          <t>Sporting</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
@@ -3199,34 +3355,34 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Siberian Husky, Boxer, Doberman Pinscher, Great Dane, Rottweiler</t>
+          <t>Golden Retriever, Labrador Retriever, Cocker Spaniel</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Terrier</t>
+          <t>Hound</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Medium-High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Yorkshire Terrier, West Highland White Terrier, Jack Russell Terrier</t>
+          <t>Beagle, Italian Greyhound</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Toy</t>
+          <t>Working</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
@@ -3234,43 +3390,43 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Chihuahua, Pomeranian, Maltese, Pug</t>
+          <t>Siberian Husky, Doberman Pinscher, Rottweiler, Great Dane</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Non-Sporting</t>
+          <t>Spitz</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Low-Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>French Bulldog, Poodle, Bulldog, Boston Terrier, Dalmatian</t>
+          <t>Shiba Inu, Samoyed</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Herding</t>
+          <t>Terrier</t>
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
@@ -3279,47 +3435,27 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>German Shepherd, Border Collie, Pembroke Welsh Corgi, Australian Shepherd</t>
+          <t>Jack Russell Terrier</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Spitz</t>
+          <t>Native &amp; Local HK</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Medium-High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Shiba Inu</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Native HK</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Tong Gau</t>
+          <t>Tong Gau, Local Mixed Breed / Rescue</t>
         </is>
       </c>
     </row>

--- a/research/breed-intelligence-database.xlsx
+++ b/research/breed-intelligence-database.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Breed Intelligence DB" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Breed Groups Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -2682,7 +2682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.44140625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -2691,6 +2691,7 @@
     <col width="31.21875" customWidth="1" style="1" min="4" max="4"/>
     <col width="35.109375" customWidth="1" style="1" min="5" max="5"/>
     <col width="26.21875" customWidth="1" style="1" min="6" max="6"/>
+    <col width="31.21875" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2724,6 +2725,11 @@
           <t>Example Breeds</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Bonding &amp; Adventure Missions</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="57.6" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -2758,6 +2764,13 @@
           <t>Dachshund, Beagle, Shiba Inu, Italian Greyhound, Jack Russell Terrier</t>
         </is>
       </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>1. Explore a park or trail you've never visited together, letting the dog choose the direction at 3 intersections. (Adventure)
+2. Follow a scent trail laid with 5 hidden treats across a new outdoor space. (Adventure)
+3. Sit together outdoors after the walk and give calm praise while the dog decompresses. (Bonding)</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="57.6" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -2792,6 +2805,13 @@
           <t>Poodle, Pembroke Welsh Corgi, German Shepherd, Border Collie, Australian Shepherd</t>
         </is>
       </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>1. Teach a new hand-signal command together, ending with a play reward. (Bonding)
+2. Play a 10-minute "find the toy" memory game indoors. (Bonding)
+3. Visit a new environment (cafe patio, new street) and practice calm focus amid novelty. (Adventure)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="57.6" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
@@ -2826,6 +2846,13 @@
           <t>Maltese, Pomeranian, Cavalier King Charles Spaniel, Bichon Frise, Golden Retriever, Cocker Spaniel, Samoyed</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>1. One-on-one cuddle/play session with their favorite person for 15 minutes. (Bonding)
+2. Supervised play date at home with a friend's dog. (Bonding)
+3. Group walk with another dog and owner to a new local spot. (Adventure)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="43.2" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
@@ -2860,6 +2887,13 @@
           <t>Siberian Husky, Samoyed</t>
         </is>
       </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>1. Hike a new trail with elevation change for at least 30 minutes. (Adventure)
+2. Try a new outdoor activity together (paddleboard, beach run, open field). (Adventure)
+3. End the adventure with a relaxed shared rest stop, water break, and praise. (Bonding)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="57.6" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -2894,6 +2928,13 @@
           <t>French Bulldog, Shih Tzu, Italian Greyhound, Great Dane, Local Mixed Breed / Rescue, Tong Gau</t>
         </is>
       </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>1. Quiet 15-minute brushing/massage session on the couch. (Bonding)
+2. Sit together in a favorite calm spot (balcony, window seat) for 10 minutes of just being present. (Bonding)
+3. A slow, unhurried walk to one new-but-quiet nearby spot, no pressure to explore far. (Adventure)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="57.6" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
@@ -2928,6 +2969,13 @@
           <t>Chihuahua, Yorkshire Terrier, Miniature Schnauzer, Doberman Pinscher, Rottweiler, Tong Gau</t>
         </is>
       </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>1. One-on-one structured training time with their primary person, ending in praise/play. (Bonding)
+2. Calm "watch duty" time together on the porch/balcony, rewarding relaxed alertness. (Bonding)
+3. Confidence-building walk to a new but controlled environment (quiet trail, empty lot). (Adventure)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="57.6" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -2962,6 +3010,13 @@
           <t>Pug, Labrador Retriever, French Bulldog, Golden Retriever, Beagle</t>
         </is>
       </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>1. Hand-feed a portion of dinner during a bonding training session. (Bonding)
+2. Make a frozen treat or puzzle together and share the "unveiling" moment. (Bonding)
+3. Visit a new dog-friendly cafe or market for supervised, treat-motivated exploration. (Adventure)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="57.6" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
@@ -2994,6 +3049,13 @@
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Jack Russell Terrier, Poodle, Border Collie, Australian Shepherd, Siberian Husky</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>1. Timed fetch/sprint session at a new open space. (Adventure)
+2. Agility or obstacle circuit at a dog park or DIY backyard course. (Adventure)
+3. Post-workout cooldown stretch/massage together. (Bonding)</t>
         </is>
       </c>
     </row>
